--- a/ksoft_old/docs/records/Operation_Code_Records.xlsx
+++ b/ksoft_old/docs/records/Operation_Code_Records.xlsx
@@ -11668,13 +11668,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7F599BF-D9CE-45B8-A172-54040F057A8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3286A201-D214-4B47-BF9C-6893F388FF67}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A448E6C-3469-4892-A9A4-61A9095541A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DA8CA8-6663-43B0-9EA8-25FBC53D8B48}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242890BB-FC32-4671-BFD8-A4BCD16DF330}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0DDBA56-F366-432E-93A5-D2388243DA27}"/>
 </file>
--- a/ksoft_old/docs/records/Operation_Code_Records.xlsx
+++ b/ksoft_old/docs/records/Operation_Code_Records.xlsx
@@ -11668,13 +11668,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3286A201-D214-4B47-BF9C-6893F388FF67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4477F7E1-C780-4870-BEA3-2098875A5198}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DA8CA8-6663-43B0-9EA8-25FBC53D8B48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D65B7483-67FF-4623-897E-8DB1531EFCDC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0DDBA56-F366-432E-93A5-D2388243DA27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7683CE4-FF8F-40C7-95E6-AA0120D40477}"/>
 </file>
--- a/ksoft_old/docs/records/Operation_Code_Records.xlsx
+++ b/ksoft_old/docs/records/Operation_Code_Records.xlsx
@@ -11668,13 +11668,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4477F7E1-C780-4870-BEA3-2098875A5198}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7F599BF-D9CE-45B8-A172-54040F057A8A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D65B7483-67FF-4623-897E-8DB1531EFCDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A448E6C-3469-4892-A9A4-61A9095541A9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7683CE4-FF8F-40C7-95E6-AA0120D40477}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242890BB-FC32-4671-BFD8-A4BCD16DF330}"/>
 </file>